--- a/backtest_runs/20260410_193731/by_symbol/PAKOXY/PAKOXY.xlsx
+++ b/backtest_runs/20260410_193731/by_symbol/PAKOXY/PAKOXY.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -538,10 +538,10 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>100000</v>
@@ -633,7 +633,7 @@
         <v>-1198.990000000004</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K4" s="3" t="n">
         <v>101620.04</v>
@@ -676,10 +676,10 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K5" s="2" t="n">
         <v>101620.04</v>
@@ -817,7 +817,7 @@
         <v>-5192.950000000007</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K8" s="3" t="n">
         <v>103284.19</v>
@@ -955,7 +955,7 @@
         <v>-4262.629999999998</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K11" s="3" t="n">
         <v>104198.47</v>
@@ -1047,7 +1047,7 @@
         <v>-3849.599999999998</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K13" s="3" t="n">
         <v>100348.87</v>
@@ -1185,7 +1185,7 @@
         <v>-2730.810000000001</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K16" s="3" t="n">
         <v>100481.2</v>
@@ -1277,7 +1277,7 @@
         <v>-2434.069999999997</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K18" s="3" t="n">
         <v>98275.7</v>
@@ -1323,7 +1323,7 @@
         <v>-1531.819999999997</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K19" s="3" t="n">
         <v>96743.88</v>
@@ -1507,7 +1507,7 @@
         <v>-3825.539999999997</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K23" s="3" t="n">
         <v>94626.59999999999</v>
@@ -1553,7 +1553,7 @@
         <v>-2125.300000000005</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K24" s="3" t="n">
         <v>92501.29999999999</v>
@@ -1645,7 +1645,7 @@
         <v>-874.1800000000028</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K26" s="3" t="n">
         <v>100810.02</v>
